--- a/api/templates/device_report/uk.xlsx
+++ b/api/templates/device_report/uk.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Зверніть увагу, що цей звіт містить результати MTB/Rif, а також MTB ULTRA</t>
+    <t xml:space="preserve">Зверніть увагу, що цей звіт містить результати MTB/Rif, MTB ULTRA та MTB XDR</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;Table&gt;</t>
@@ -456,7 +456,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.21484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="30.58"/>

--- a/api/templates/device_report/uk.xlsx
+++ b/api/templates/device_report/uk.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t xml:space="preserve">Пристрої GeneXpert</t>
   </si>
@@ -59,6 +59,18 @@
   </si>
   <si>
     <t xml:space="preserve"># MTB-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># MTB+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># MTB Trace Detected</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Помилка MTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># MTB Недійсний</t>
   </si>
   <si>
     <t xml:space="preserve"># MTB+ RIF
@@ -72,15 +84,6 @@
     <t xml:space="preserve"># MTB+ RIF невизначений</t>
   </si>
   <si>
-    <t xml:space="preserve"># результати помилок</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># недійсні результати</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># ніякого результату</t>
-  </si>
-  <si>
     <t xml:space="preserve"># INH</t>
   </si>
   <si>
@@ -99,11 +102,7 @@
     <t xml:space="preserve"># ETH</t>
   </si>
   <si>
-    <t xml:space="preserve"># Xpert
-використовувані модулі</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кількість днів перервана служба</t>
+    <t xml:space="preserve"># Використовувані модулі</t>
   </si>
   <si>
     <t xml:space="preserve">Причина переривання</t>
@@ -118,7 +117,7 @@
     <t xml:space="preserve">коментар</t>
   </si>
   <si>
-    <t xml:space="preserve"># загальні тести Xpert</t>
+    <t xml:space="preserve"># Всього тестів</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;name&gt;</t>
@@ -139,6 +138,21 @@
     <t xml:space="preserve">&lt;totalMtbNegative&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">&lt;totalMtbDetected&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;totalMtbTraceDetected&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;totalErrors&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;mtbInvalid&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;mtbNoResult&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;totalMtbSens&gt;</t>
   </si>
   <si>
@@ -146,15 +160,6 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;totalMtbIndeterminate&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;totalErrors&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;mtbInvalid&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;mtbNoResult&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;INH&gt;</t>
@@ -455,20 +460,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultColWidth="11.21484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AA14"/>
+  <sheetFormatPr defaultColWidth="11.234375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="30.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="11.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="13" style="0" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="1" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="33.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="20.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="11.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="15.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="15" style="0" width="15.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="0" width="20.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="24" style="1" width="20.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="33.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="20.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -531,10 +536,10 @@
       <c r="F10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="7" t="s">
@@ -544,48 +549,54 @@
         <v>16</v>
       </c>
       <c r="K10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="M10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="N10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="O10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="P10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="Q10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Q10" s="7" t="s">
+      <c r="R10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="S10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="S10" s="8" t="s">
+      <c r="T10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="T10" s="8" t="s">
+      <c r="U10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="U10" s="7" t="s">
+      <c r="V10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="W10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="V10" s="9" t="s">
+      <c r="X10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="W10" s="9" t="s">
+      <c r="Y10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="X10" s="7" t="s">
+      <c r="Z10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="Y10" s="7" t="s">
+      <c r="AA10" s="7" t="s">
         <v>31</v>
       </c>
     </row>
@@ -614,7 +625,7 @@
       <c r="H11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="12" t="s">
         <v>40</v>
       </c>
       <c r="J11" s="12" t="s">
@@ -623,13 +634,13 @@
       <c r="K11" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="12" t="s">
+      <c r="N11" s="11" t="s">
         <v>45</v>
       </c>
       <c r="O11" s="12" t="s">
@@ -644,29 +655,35 @@
       <c r="R11" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="S11" s="11" t="s">
+      <c r="S11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="T11" s="11" t="s">
+      <c r="T11" s="12" t="s">
         <v>51</v>
       </c>
       <c r="U11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="V11" s="13" t="e">
-        <f aca="false">IF(Y11=0,0,J11/Y11)</f>
+      <c r="V11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="X11" s="13" t="e">
+        <f aca="false">IF(AA11=0,0,I11/AA11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W11" s="14" t="e">
-        <f aca="false">IF(Y11=0,0,(J11+K11)/Y11)</f>
+      <c r="Y11" s="14" t="e">
+        <f aca="false">IF(AA11=0,0,(I11+J11)/AA11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X11" s="14" t="e">
-        <f aca="false">IF(W11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
+      <c r="Z11" s="14" t="e">
+        <f aca="false">IF(Y11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Y11" s="11" t="s">
-        <v>53</v>
+      <c r="AA11" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/api/templates/device_report/uk.xlsx
+++ b/api/templates/device_report/uk.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t xml:space="preserve">Пристрої GeneXpert</t>
   </si>
@@ -28,16 +28,28 @@
     <t xml:space="preserve">Дати: &lt;Dates&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">Примітки</t>
+  </si>
+  <si>
     <t xml:space="preserve">Області: &lt;States&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">Зверніть увагу, що цей звіт містить результати MTB/Rif, MTB ULTRA та MTB XDR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Райони: &lt;Lgas&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Зверніть увагу, що цей звіт містить результати MTB/Rif, MTB ULTRA та MTB XDR</t>
+    <t xml:space="preserve">Список літератури</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Використовувані модулі</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Підраховує кількість днів, коли пристрій принаймні один раз повідомлялося про будь-який із статусів неактивності (включно зі статусами «Невідомо» та «Тестування не проводилися»).</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;Table&gt;</t>
@@ -102,7 +114,7 @@
     <t xml:space="preserve"># ETH</t>
   </si>
   <si>
-    <t xml:space="preserve"># Використовувані модулі</t>
+    <t xml:space="preserve"># Модулі, використані в діапазоні дат</t>
   </si>
   <si>
     <t xml:space="preserve">Причина переривання</t>
@@ -318,7 +330,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -332,11 +344,23 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -460,11 +484,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA14"/>
-  <sheetFormatPr defaultColWidth="11.234375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AA1048576"/>
+  <sheetFormatPr defaultColWidth="11.29296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="30.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="11.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="15.57"/>
@@ -488,211 +514,231 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C2" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
+      <c r="A8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" s="10" customFormat="true" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" s="13" customFormat="true" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="R10" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="S10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="V10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="S10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="V10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="W10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="X10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA10" s="7" t="s">
+      <c r="W10" s="10" t="s">
         <v>31</v>
       </c>
+      <c r="X10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA10" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="11" t="s">
+      <c r="A11" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="B11" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="C11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="D11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="E11" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="F11" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="G11" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="H11" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="I11" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="J11" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="K11" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="12" t="s">
+      <c r="L11" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="Q11" s="12" t="s">
+      <c r="M11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="R11" s="12" t="s">
+      <c r="N11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="S11" s="12" t="s">
+      <c r="O11" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="T11" s="12" t="s">
+      <c r="P11" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="U11" s="11" t="s">
+      <c r="Q11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="V11" s="11" t="s">
+      <c r="R11" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="W11" s="11" t="s">
+      <c r="S11" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="X11" s="13" t="e">
+      <c r="T11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="V11" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="W11" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="X11" s="16" t="e">
         <f aca="false">IF(AA11=0,0,I11/AA11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Y11" s="14" t="e">
+      <c r="Y11" s="17" t="e">
         <f aca="false">IF(AA11=0,0,(I11+J11)/AA11)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Z11" s="14" t="e">
+      <c r="Z11" s="17" t="e">
         <f aca="false">IF(Y11&gt;0.05,"Високий рівень помилок/недійсних даних. Звертайтесь до лаб.","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA11" s="11" t="s">
-        <v>55</v>
+      <c r="AA11" s="14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-    </row>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C3:D3"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
